--- a/Carga Masiva/CargaMaterialesAcrux.xlsx
+++ b/Carga Masiva/CargaMaterialesAcrux.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RepositoriosAEC\Acrux-Release\Carga Masiva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{1FCF862C-B448-4B10-8F32-71BC34FFC7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DBA437-2EF3-4626-BB1D-816B5F5FA4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CargaMaterialesAcrux" sheetId="1" r:id="rId1"/>
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -297,7 +297,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,6 +475,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -638,8 +644,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -994,25 +1001,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -1027,31 +1034,31 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -1063,7 +1070,7 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -1113,31 +1120,31 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>500</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>1000</v>
       </c>
       <c r="L2">
@@ -1149,7 +1156,7 @@
       <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>100</v>
       </c>
       <c r="P2">

--- a/Carga Masiva/CargaMaterialesAcrux.xlsx
+++ b/Carga Masiva/CargaMaterialesAcrux.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RepositoriosAEC\Acrux-Release\Carga Masiva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DBA437-2EF3-4626-BB1D-816B5F5FA4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEBD4F3-75CC-414E-8FA1-519A320412C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CargaMaterialesAcrux" sheetId="1" r:id="rId1"/>
@@ -58,12 +58,6 @@
     <t>PRECIO MIN</t>
   </si>
   <si>
-    <t>PORCENTAJE IMPUESTO</t>
-  </si>
-  <si>
-    <t>BASE GRAVABLE</t>
-  </si>
-  <si>
     <t>STOCK</t>
   </si>
   <si>
@@ -155,6 +149,12 @@
   </si>
   <si>
     <t>AD10</t>
+  </si>
+  <si>
+    <t>CLASE IMPUESTO</t>
+  </si>
+  <si>
+    <t>IMP001</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -1018,16 +1018,15 @@
     <col min="11" max="11" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="27" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="26" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1065,55 +1064,52 @@
         <v>11</v>
       </c>
       <c r="M1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1121,25 +1117,25 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="J2" s="1">
         <v>500</v>
@@ -1150,53 +1146,50 @@
       <c r="L2">
         <v>500</v>
       </c>
-      <c r="M2">
-        <v>18</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1">
+      <c r="M2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="1">
         <v>100</v>
       </c>
+      <c r="O2">
+        <v>50</v>
+      </c>
       <c r="P2">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="Q2">
-        <v>150</v>
-      </c>
-      <c r="R2">
         <v>1</v>
       </c>
+      <c r="R2" t="s">
+        <v>33</v>
+      </c>
       <c r="S2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" t="s">
         <v>35</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>36</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>37</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>38</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>39</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>40</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>41</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>42</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Carga Masiva/CargaMaterialesAcrux.xlsx
+++ b/Carga Masiva/CargaMaterialesAcrux.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RepositoriosAEC\Acrux-Release\Carga Masiva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEBD4F3-75CC-414E-8FA1-519A320412C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7FA1DA-CD53-4A21-8144-D2715DC9B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>TIPO INVENTARIO</t>
   </si>
@@ -155,6 +155,15 @@
   </si>
   <si>
     <t>IMP001</t>
+  </si>
+  <si>
+    <t>ID_CENTRO</t>
+  </si>
+  <si>
+    <t>ID_ALMACEN</t>
+  </si>
+  <si>
+    <t>UBICACION</t>
   </si>
 </sst>
 </file>
@@ -644,9 +653,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1002,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -1026,90 +1037,99 @@
     <col min="27" max="27" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>

--- a/Carga Masiva/CargaMaterialesAcrux.xlsx
+++ b/Carga Masiva/CargaMaterialesAcrux.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RepositoriosAEC\Acrux-Release\Carga Masiva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7FA1DA-CD53-4A21-8144-D2715DC9B6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB4C9A4-BA92-4AA4-ACAE-15E9A09F3DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CargaMaterialesAcrux" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>TIPO INVENTARIO</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>UBICACION</t>
+  </si>
+  <si>
+    <t>0-0-0</t>
   </si>
 </sst>
 </file>
@@ -1211,6 +1214,15 @@
       <c r="AA2" t="s">
         <v>42</v>
       </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
